--- a/output/pdf_financials_xlsx/SEAS.xlsx
+++ b/output/pdf_financials_xlsx/SEAS.xlsx
@@ -431,6 +431,12 @@
   </sheetPr>
   <dimension ref="A1:D135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="56" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">

--- a/output/pdf_financials_xlsx/SEAS.xlsx
+++ b/output/pdf_financials_xlsx/SEAS.xlsx
@@ -485,15 +485,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -502,18 +498,16 @@
           <t xml:space="preserve">  Cost of Goods Sold</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -527,15 +521,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -544,18 +534,16 @@
           <t xml:space="preserve">  Selling, General, &amp; Admin. Expense</t>
         </is>
       </c>
-      <c r="B7" s="3" t="n">
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>0.083721</v>
       </c>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D7" s="3" t="n">
+        <v>0.136744</v>
       </c>
     </row>
     <row r="8">
@@ -564,18 +552,16 @@
           <t xml:space="preserve">  Research &amp; Development</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -584,18 +570,16 @@
           <t xml:space="preserve">  Other Operating Expense</t>
         </is>
       </c>
-      <c r="B9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>0.030676</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>0.07439800000000001</v>
       </c>
     </row>
     <row r="10">
@@ -604,18 +588,16 @@
           <t xml:space="preserve">  Total Operating Expense</t>
         </is>
       </c>
-      <c r="B10" s="3" t="n">
-        <v>0.083721</v>
-      </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>0.114397</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>0.211142</v>
       </c>
     </row>
     <row r="11">
@@ -629,15 +611,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C11" s="3" t="n">
+        <v>-0.114397</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>-0.211142</v>
       </c>
     </row>
     <row r="12">
@@ -646,18 +624,16 @@
           <t xml:space="preserve">    Interest Income</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>0.007558</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>0.005433</v>
       </c>
     </row>
     <row r="13">
@@ -666,18 +642,16 @@
           <t xml:space="preserve">    Interest Expense</t>
         </is>
       </c>
-      <c r="B13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B13" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="14">
@@ -686,18 +660,16 @@
           <t xml:space="preserve">  Net Interest Income</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B14" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -706,18 +678,16 @@
           <t xml:space="preserve">  Other Income (Expense)</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B15" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>-9e-06</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>-0.001475</v>
       </c>
     </row>
     <row r="16">
@@ -731,15 +701,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C16" s="3" t="n">
+        <v>-0.11482</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>-0.314169</v>
       </c>
     </row>
     <row r="17">
@@ -748,18 +714,16 @@
           <t xml:space="preserve">  Tax Provision</t>
         </is>
       </c>
-      <c r="B17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B17" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="18">
@@ -817,15 +781,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C20" s="3" t="n">
+        <v>-0.11482</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>-0.314169</v>
       </c>
     </row>
     <row r="21">
@@ -834,18 +794,16 @@
           <t xml:space="preserve">    Net Income (Discontinued Operations)</t>
         </is>
       </c>
-      <c r="B21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B21" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -854,18 +812,16 @@
           <t xml:space="preserve">  Other Income (Minority Interest)</t>
         </is>
       </c>
-      <c r="B22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B22" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -879,15 +835,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C23" s="3" t="n">
+        <v>-0.11482</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>-0.314169</v>
       </c>
     </row>
     <row r="24">
@@ -901,15 +853,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C24" s="3" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>-0.02</v>
       </c>
     </row>
     <row r="25">
@@ -923,15 +871,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C25" s="3" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>-0.02</v>
       </c>
     </row>
     <row r="26">
@@ -950,10 +894,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D26" s="3" t="n">
+        <v>15.70845</v>
       </c>
     </row>
     <row r="27">
@@ -967,15 +909,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C27" s="3" t="n">
+        <v>-0.122378</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>-0.319602</v>
       </c>
     </row>
     <row r="28">
@@ -984,18 +922,16 @@
           <t xml:space="preserve">  Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B28" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B28" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -1009,15 +945,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C29" s="3" t="n">
+        <v>-0.122378</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>-0.319602</v>
       </c>
     </row>
     <row r="30">
@@ -1053,15 +985,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C31" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -2271,15 +2199,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C99" s="3" t="n">
+        <v>-0.11482</v>
+      </c>
+      <c r="D99" s="3" t="n">
+        <v>-0.314169</v>
       </c>
     </row>
     <row r="100">
@@ -2293,15 +2217,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D100" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -2315,15 +2235,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C101" s="3" t="n">
+        <v>-0.00759</v>
+      </c>
+      <c r="D101" s="3" t="n">
+        <v>0.023777</v>
       </c>
     </row>
     <row r="102">
@@ -2337,15 +2253,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D102" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -2359,15 +2271,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D103" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -2381,15 +2289,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C104" s="3" t="n">
+        <v>0.074753</v>
+      </c>
+      <c r="D104" s="3" t="n">
+        <v>0.009686999999999999</v>
       </c>
     </row>
     <row r="105">
@@ -2403,15 +2307,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D105" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -2425,15 +2325,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C106" s="3" t="n">
+        <v>0.067163</v>
+      </c>
+      <c r="D106" s="3" t="n">
+        <v>0.033464</v>
       </c>
     </row>
     <row r="107">
@@ -2447,15 +2343,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D107" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -2469,15 +2361,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D108" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -2491,15 +2379,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D109" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -2513,15 +2397,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D110" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -2535,15 +2415,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D111" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -2557,15 +2433,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D112" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -2579,15 +2451,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D113" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -2601,15 +2469,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D114" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -2623,15 +2487,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D115" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -2645,15 +2505,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D116" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -2667,15 +2523,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D117" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -2689,15 +2541,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D118" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -2716,10 +2564,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D119" s="3" t="n">
+        <v>-0.025</v>
       </c>
     </row>
     <row r="120">
@@ -2733,15 +2579,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D120" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -2755,15 +2597,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D121" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -2777,15 +2615,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D122" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -2799,15 +2633,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D123" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -2821,15 +2651,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D124" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -2843,15 +2669,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D125" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -2865,15 +2687,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D126" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -2909,15 +2727,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D128" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -2936,10 +2750,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D129" s="3" t="n">
+        <v>0.09225</v>
       </c>
     </row>
     <row r="130">
@@ -2953,15 +2765,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C130" s="3" t="n">
+        <v>0.257847</v>
+      </c>
+      <c r="D130" s="3" t="n">
+        <v>0.21019</v>
       </c>
     </row>
     <row r="131">
@@ -2975,15 +2783,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D131" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -2997,15 +2801,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C132" s="3" t="n">
+        <v>-0.047657</v>
+      </c>
+      <c r="D132" s="3" t="n">
+        <v>-0.110455</v>
       </c>
     </row>
     <row r="133">
@@ -3019,15 +2819,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C133" s="3" t="n">
+        <v>0.21019</v>
+      </c>
+      <c r="D133" s="3" t="n">
+        <v>0.099735</v>
       </c>
     </row>
     <row r="134">
@@ -3041,15 +2837,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D134" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -3063,15 +2855,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C135" s="3" t="n">
+        <v>-0.047657</v>
+      </c>
+      <c r="D135" s="3" t="n">
+        <v>-0.177705</v>
       </c>
     </row>
   </sheetData>
@@ -3085,7 +2873,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3528,83 +3316,81 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Operating Expenses</t>
+          <t>Cash Flows Used in Operating Activities</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Professional and consulting fees (Note 9) 131,617</t>
+          <t>Net loss for the year</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="n">
-        <v>0.083116</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-0.11482</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>-0.314169</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Operating Expenses</t>
+          <t>Adjustments for non-cash items</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Listing and filing fees 74,398</t>
+          <t>Write-down of mineral property interests (Note 5)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
-      <c r="E15" s="5" t="n">
-        <v>0.030676</v>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G15" s="5" t="n">
+        <v>0.103</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Operating Expenses</t>
+          <t>Adjustments for non-cash items</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Travel, meals and entertainment 9,578</t>
+          <t>Adjustments for non-cash items total</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -3613,131 +3399,133 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F16" s="5" t="n">
+        <v>-0.11482</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>-0.211169</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Operating Expenses</t>
+          <t>Changes in non-cash working capital</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Office and general 5,127</t>
+          <t>Other receivables</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="n">
-        <v>0.000605</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-0.00759</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>0.023777</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Operating Expenses</t>
+          <t>Changes in non-cash working capital</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Exploration and evaluation expenditures (recoveries) (Note 10) (5,593)</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" s="5" t="n">
-        <v>0.007972</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Accounts payable and accrued liabilities</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>0.074753</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>0.009686999999999999</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Operating Expenses</t>
+          <t>Changes in non-cash working capital</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Operating Loss before the Undernoted (215,127)</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" s="5" t="n">
-        <v>-0.122369</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash Flows used in Operating Activities</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>-0.047657</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>-0.177705</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Other Income (Expenses)</t>
+          <t>Cash Flows from Financing Activities</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Write-down of mineral property interests (Note 5) (103,000)</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>Proceeds from issuance of common shares (Note 7)</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>-</t>
@@ -3748,221 +3536,235 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G20" s="5" t="n">
+        <v>0.09225</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Other Income (Expenses)</t>
+          <t>Cash Flows from Financing Activities</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Finance income 5,433</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" s="5" t="n">
-        <v>0.007558</v>
+          <t>Cash Flows provided by Financing Activities</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G21" s="5" t="n">
+        <v>0.09225</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Other Income (Expenses)</t>
+          <t>Cash Flows from Investing Activities</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Foreign exchange loss (1,475)</t>
+          <t>Payment pursuant to Twilite Gold Project option agreement (Note 5)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
-      <c r="E22" s="5" t="n">
-        <v>-9e-06</v>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G22" s="5" t="n">
+        <v>-0.025</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Other Income (Expenses)</t>
+          <t>Cash Flows from Investing Activities</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Net Loss and Comprehensive Loss (314,169)</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" s="5" t="n">
-        <v>-0.11482</v>
+          <t>Cash Flows used in Investing Activities</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G23" s="5" t="n">
+        <v>-0.025</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Other Income (Expenses)</t>
+          <t>Cash Flows from Investing Activities</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Weighted Average Number of Shares Outstanding 13,124,960</t>
+          <t>Decrease in cash and cash equivalents</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>BasicAverageShares</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="n">
-        <v>11.8237</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>-0.047657</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>-0.110455</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Other Income (Expenses)</t>
+          <t>Cash Flows from Investing Activities</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Net Loss per Share – basic and diluted (0.02)</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" s="5" t="n">
-        <v>-1e-08</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash and cash equivalents, beginning of year</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>0.257847</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>0.21019</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Cash Flows from Investing Activities</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2023 11,823,700 705,438 77,849 (519,060)</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" s="5" t="n">
-        <v>0.264227</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash and cash equivalents, end of year</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>0.21019</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>0.099735</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Supplemental Information</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Net loss for the year - - - (114,820)</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" s="5" t="n">
-        <v>-0.11482</v>
+          <t>Income tax paid</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>IncomeTaxPaidSupplementalData</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3978,53 +3780,59 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Supplemental Information</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2024 11,823,700 705,438 77,849 (633,880)</t>
+          <t>Mining exploration tax credit received (Note 10)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
-      <c r="E28" s="5" t="n">
-        <v>0.149407</v>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G28" s="5" t="n">
+        <v>0.012813</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Supplemental Information</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Issuance of shares from private placement (Note 7) 1,230,000 92,250 - -</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" s="5" t="n">
-        <v>0.09225</v>
+          <t>Interest paid</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>InterestPaidSupplementalData</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4040,32 +3848,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Non-Cash Activities</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Issuance of shares pursuant to option agreement (Notes 5 and 7) 300,000 25,500 - -</t>
+          <t>Shares issued for mineral property interests (Note 5)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
-      <c r="E30" s="5" t="n">
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="n">
         <v>0.0255</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
     </row>
     <row r="31">
@@ -4076,29 +3884,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Operating Expenses</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Cancellation of stock options (Note 8) - - (63,876) 63,876</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
+          <t>Professional and consulting fees (Note 9)</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F31" s="5" t="n">
+        <v>0.083116</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>0.131617</v>
       </c>
     </row>
     <row r="32">
@@ -4109,27 +3917,29 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Operating Expenses</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Net loss for the year - - - (314,169)</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" s="5" t="n">
-        <v>-0.314169</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Listing and filing fees</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>0.030676</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>0.07439800000000001</v>
       </c>
     </row>
     <row r="33">
@@ -4140,27 +3950,527 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
+          <t>Operating Expenses</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Travel, meals and entertainment</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>0.009578</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Operating Expenses</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Office and general</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="n">
+        <v>0.000605</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>0.005127</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Operating Expenses</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Exploration and evaluation expenditures (recoveries) (Note 10)</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>0.007972</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>-0.005593</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Operating Expenses</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Operating Loss before the Undernoted</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="n">
+        <v>-0.122369</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>-0.215127</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Other Income (Expenses)</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Write-down of mineral property interests (Note 5)</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>-0.103</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Other Income (Expenses)</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Finance income</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="n">
+        <v>0.007558</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>0.005433</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Other Income (Expenses)</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Foreign exchange loss</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="n">
+        <v>-9e-06</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>-0.001475</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Other Income (Expenses)</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Net Loss and Comprehensive Loss</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="n">
+        <v>-0.11482</v>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>-0.314169</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Other Income (Expenses)</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Weighted Average Number of Shares Outstanding</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="n">
+        <v>11.8237</v>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>13.12496</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Other Income (Expenses)</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Net Loss per Share – basic and diluted</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>-2e-08</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Balance, December 31, 2025 13,353,700 823,188 13,973 (884,173)</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" s="5" t="n">
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Balance, December 31, 2023 11,823,700 705,438 77,849</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="n">
+        <v>0.264227</v>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>-0.51906</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Net loss for the year - - -</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="n">
+        <v>-0.11482</v>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>-0.11482</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Balance, December 31, 2024 11,823,700 705,438 77,849</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="n">
+        <v>0.149407</v>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>-0.63388</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Issuance of shares from private placement (Note 7) 1,230,000 92,250 -</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="n">
+        <v>0.09225</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Issuance of shares pursuant to option agreement (Notes 5 and 7) 300,000 25,500 -</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="n">
+        <v>0.0255</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Cancellation of stock options (Note 8) - - (63,876)</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>0.063876</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Balance, December 31, 2025 13,353,700 823,188 13,973</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="n">
         <v>-0.047012</v>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G49" s="5" t="n">
+        <v>-0.884173</v>
       </c>
     </row>
   </sheetData>

--- a/output/pdf_financials_xlsx/SEAS.xlsx
+++ b/output/pdf_financials_xlsx/SEAS.xlsx
@@ -1577,10 +1577,10 @@
         </is>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.080289</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.127657</v>
       </c>
     </row>
     <row r="65">
@@ -1631,10 +1631,10 @@
         </is>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.06162</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.023939</v>
       </c>
     </row>
     <row r="68">
